--- a/results/greedy/UAVs5_GRID13/tour/UAVs5_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs5_GRID13/tour/UAVs5_GRID13_1920_16_Greedy_sequences.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02371833298821002</v>
+        <v>0.02296962501714006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832600002875552</v>
+        <v>0.02785950002726167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761345799081028</v>
+        <v>0.02710983296856284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03124062501592562</v>
+        <v>0.03039020899450406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04739941697334871</v>
+        <v>0.04430641699582338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03436895797494799</v>
+        <v>0.03335133299697191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0312752079917118</v>
+        <v>0.02997954201418906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03481470898259431</v>
+        <v>0.03344879200449213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02677362499525771</v>
+        <v>0.0259322079946287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02609362499788404</v>
+        <v>0.02525433403206989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02898791700135916</v>
+        <v>0.02852349996101111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028775000711903</v>
+        <v>0.0293934170040302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02800141600891948</v>
+        <v>0.02698595798574388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03607129195006564</v>
+        <v>0.03562583401799202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02927362499758601</v>
+        <v>0.02830870798788965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02787758299382403</v>
+        <v>0.02691191696794704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03403575002448633</v>
+        <v>0.0337352910428308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02455037500476465</v>
+        <v>0.02387729199836031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02302095899358392</v>
+        <v>0.02236025000456721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02723020798293874</v>
+        <v>0.02639541699318215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03069054201478139</v>
+        <v>0.02968791598686948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03495754196774215</v>
+        <v>0.03354954102542251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03219445800641552</v>
+        <v>0.03122183296363801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03194479201920331</v>
+        <v>0.03072525002062321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03282795799896121</v>
+        <v>0.03181895799934864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0335139170056209</v>
+        <v>0.03293145797215402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02694404195062816</v>
+        <v>0.02693495899438858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02671745896805078</v>
+        <v>0.02664383297087625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02767575002508238</v>
+        <v>0.02751345897559077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02641037496505305</v>
+        <v>0.0259280419559218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02157820895081386</v>
+        <v>0.02118537499336526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03634083300130442</v>
+        <v>0.03646637499332428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02890108403516933</v>
+        <v>0.02798487496329471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717583300545812</v>
+        <v>0.02660954103339463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02787900000112131</v>
+        <v>0.02765812497818843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02636424999218434</v>
+        <v>0.0257404160220176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02389308396959677</v>
+        <v>0.02317608403973281</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03636566700879484</v>
+        <v>0.03507179202279076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02737920900108293</v>
+        <v>0.02633300004526973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03434175002621487</v>
+        <v>0.03336937498534098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03453499998431653</v>
+        <v>0.03379716700874269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0291578330215998</v>
+        <v>0.02824916603276506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303737500915304</v>
+        <v>0.02260154101531953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02504216600209475</v>
+        <v>0.02481812500627711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03067704098066315</v>
+        <v>0.02965883305296302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03748912503942847</v>
+        <v>0.0366898329812102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558679197682068</v>
+        <v>0.02472883299924433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03374949999852106</v>
+        <v>0.03284212504513562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03130387497367337</v>
+        <v>0.03021104197250679</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922766702249646</v>
+        <v>0.02883354196092114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03636204195208848</v>
+        <v>0.03544066700851545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02905862499028444</v>
+        <v>0.02829062502132729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02290879201609641</v>
+        <v>0.02254166599595919</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02619174995925277</v>
+        <v>0.02496908296598122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03074633301002905</v>
+        <v>0.02951025002403185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03413541696500033</v>
+        <v>0.03315412497613579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03075808298308402</v>
+        <v>0.03016537497751415</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0305797919863835</v>
+        <v>0.02980858297087252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0263309589936398</v>
+        <v>0.02632141701178625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03236550005385652</v>
+        <v>0.03124550002394244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0351290829712525</v>
+        <v>0.0353482500067912</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03326012496836483</v>
+        <v>0.03266979096224532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03305979195283726</v>
+        <v>0.03210095799295232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03286204196047038</v>
+        <v>0.03255745803471655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03569275001063943</v>
+        <v>0.03469141601817682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03184591699391603</v>
+        <v>0.03123491600854322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03509329201187938</v>
+        <v>0.03407458297442645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03391974995611235</v>
+        <v>0.03299354098271579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02861037495313212</v>
+        <v>0.02799358399352059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02708570897812024</v>
+        <v>0.02627770899562165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02370429097209126</v>
+        <v>0.02278250001836568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02699941699393094</v>
+        <v>0.02607899997383356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02571208297740668</v>
+        <v>0.02555354096693918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03269091597758234</v>
+        <v>0.03198129194788635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02859125001123175</v>
+        <v>0.027844957949128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630416600732133</v>
+        <v>0.0252022499917075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03961891605285928</v>
+        <v>0.03819999995175749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02309099998092279</v>
+        <v>0.02236833301139995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02647320798132569</v>
+        <v>0.0258497089962475</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03294850001111627</v>
+        <v>0.03280845802510157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03179162496235222</v>
+        <v>0.0313315829844214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02531883300980553</v>
+        <v>0.02482945797964931</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911587501876056</v>
+        <v>0.02820012503070757</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02293670800281689</v>
+        <v>0.02222570800222456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02849870797945186</v>
+        <v>0.02820991701446474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598824998131022</v>
+        <v>0.02530595799908042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02863604197045788</v>
+        <v>0.02782004099572077</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02248341700760648</v>
+        <v>0.02197454200359061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02356975001748651</v>
+        <v>0.02292516600573435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02438262500800192</v>
+        <v>0.02470012503908947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03454854199662805</v>
+        <v>0.03383512498112395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03509745799237862</v>
+        <v>0.03474637499311939</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03119908401276916</v>
+        <v>0.02993599994806573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03349183301907033</v>
+        <v>0.03242479200707749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02210862498031929</v>
+        <v>0.02142804197501391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02506874996470287</v>
+        <v>0.0244945419835858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02748954197159037</v>
+        <v>0.0267518749460578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03269070800160989</v>
+        <v>0.03209562500705943</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0297209580312483</v>
+        <v>0.02926733298227191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0328241249662824</v>
+        <v>0.03194041701499373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs5_GRID13/tour/UAVs5_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs5_GRID13/tour/UAVs5_GRID13_1920_16_Greedy_sequences.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02296962501714006</v>
+        <v>0.02334924996830523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02785950002726167</v>
+        <v>0.02768766699591652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02710983296856284</v>
+        <v>0.02720412501366809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03039020899450406</v>
+        <v>0.03054866701131687</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04430641699582338</v>
+        <v>0.04449166700942442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03335133299697191</v>
+        <v>0.0333838330116123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02997954201418906</v>
+        <v>0.03027587500400841</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03344879200449213</v>
+        <v>0.03412612498505041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0259322079946287</v>
+        <v>0.025954750017263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02525433403206989</v>
+        <v>0.0249991660239175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02852349996101111</v>
+        <v>0.02846295799827203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293934170040302</v>
+        <v>0.02895370800979435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02698595798574388</v>
+        <v>0.02756562503054738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03562583401799202</v>
+        <v>0.03514316596556455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02830870798788965</v>
+        <v>0.02817020803922787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02691191696794704</v>
+        <v>0.0270781249855645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0337352910428308</v>
+        <v>0.03318216599291191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387729199836031</v>
+        <v>0.02396137500181794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236025000456721</v>
+        <v>0.02251245797378942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02639541699318215</v>
+        <v>0.02659429202321917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02968791598686948</v>
+        <v>0.02957787498598918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03354954102542251</v>
+        <v>0.03437370801111683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03122183296363801</v>
+        <v>0.03107999998610467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072525002062321</v>
+        <v>0.03099858295172453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03181895799934864</v>
+        <v>0.03199245798168704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03293145797215402</v>
+        <v>0.03284904098836705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02693495899438858</v>
+        <v>0.02613483398454264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02664383297087625</v>
+        <v>0.02586820797296241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02751345897559077</v>
+        <v>0.02678812498925254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0259280419559218</v>
+        <v>0.02551549999043345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118537499336526</v>
+        <v>0.02099370898213238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03646637499332428</v>
+        <v>0.03617691603722051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02798487496329471</v>
+        <v>0.02817895798943937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02660954103339463</v>
+        <v>0.02668345900019631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02765812497818843</v>
+        <v>0.02751074999105185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0257404160220176</v>
+        <v>0.0259312919806689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02317608403973281</v>
+        <v>0.02318629197543487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03507179202279076</v>
+        <v>0.03577145800227299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02633300004526973</v>
+        <v>0.02668816701043397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03336937498534098</v>
+        <v>0.03331216605147347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03379716700874269</v>
+        <v>0.03352708299644291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02824916603276506</v>
+        <v>0.02840387501055375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02260154101531953</v>
+        <v>0.02263079100521281</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02481812500627711</v>
+        <v>0.02488670800812542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02965883305296302</v>
+        <v>0.030069625005126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0366898329812102</v>
+        <v>0.03590216703014448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02472883299924433</v>
+        <v>0.02478358300868422</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03284212504513562</v>
+        <v>0.03323620901210234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03021104197250679</v>
+        <v>0.0306281250086613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02883354196092114</v>
+        <v>0.02881450002314523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03544066700851545</v>
+        <v>0.03581816703081131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02829062502132729</v>
+        <v>0.0287592500098981</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254166599595919</v>
+        <v>0.02234608394792303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02496908296598122</v>
+        <v>0.02563845796976238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02951025002403185</v>
+        <v>0.02968408295419067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03315412497613579</v>
+        <v>0.03351812501205131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03016537497751415</v>
+        <v>0.02973004203522578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02980858297087252</v>
+        <v>0.02973562496481463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02632141701178625</v>
+        <v>0.02613958297297359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03124550002394244</v>
+        <v>0.03147854097187519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0353482500067912</v>
+        <v>0.03498774999752641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03266979096224532</v>
+        <v>0.032430374994874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03210095799295232</v>
+        <v>0.03255479200743139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03255745803471655</v>
+        <v>0.03240995900705457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03469141601817682</v>
+        <v>0.03474683302920312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03123491600854322</v>
+        <v>0.03107199998339638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03407458297442645</v>
+        <v>0.03415349998977035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03299354098271579</v>
+        <v>0.03335691697429866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02799358399352059</v>
+        <v>0.02795733301900327</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627770899562165</v>
+        <v>0.02666408300865442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02278250001836568</v>
+        <v>0.02321545901941136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02607899997383356</v>
+        <v>0.02621529099997133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02555354096693918</v>
+        <v>0.02538320800522342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03198129194788635</v>
+        <v>0.03153208398725837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.027844957949128</v>
+        <v>0.02798204100690782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252022499917075</v>
+        <v>0.02540325000882149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03819999995175749</v>
+        <v>0.03855708299670368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236833301139995</v>
+        <v>0.02246200002264231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0258497089962475</v>
+        <v>0.02585000003455207</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03280845802510157</v>
+        <v>0.03260045900242403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0313315829844214</v>
+        <v>0.03113908402156085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02482945797964931</v>
+        <v>0.02476054197177291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02820012503070757</v>
+        <v>0.02847537497291341</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02222570800222456</v>
+        <v>0.02224458300042897</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02820991701446474</v>
+        <v>0.02818387496517971</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02530595799908042</v>
+        <v>0.02532600000267848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02782004099572077</v>
+        <v>0.02790250000543892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02197454200359061</v>
+        <v>0.02204266702756286</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02292516600573435</v>
+        <v>0.02311270800419152</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02470012503908947</v>
+        <v>0.02368883299641311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03383512498112395</v>
+        <v>0.03394699998898432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03474637499311939</v>
+        <v>0.03464699996402487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02993599994806573</v>
+        <v>0.03029370802687481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03242479200707749</v>
+        <v>0.03281933401012793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02142804197501391</v>
+        <v>0.02162862499244511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0244945419835858</v>
+        <v>0.02472941600717604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0267518749460578</v>
+        <v>0.02711720898514614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03209562500705943</v>
+        <v>0.03199595800833777</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02926733298227191</v>
+        <v>0.0294174169539474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03194041701499373</v>
+        <v>0.03234491701005027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
